--- a/LegalSystem/Templates/CasesDashboard.xlsx
+++ b/LegalSystem/Templates/CasesDashboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.sanad\Downloads\LegalSystem-BE\LegalSystem\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\LegalSystem-BE\LegalSystem\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFE00E1-23FF-44BE-A134-46B91AA789AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAB5E1D-F03B-4EB8-A5A2-EB9DA63046D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOC Handover Appointments" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">Report Generated On: </t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Level</t>
   </si>
   <si>
     <t>Court</t>
@@ -184,6 +181,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -192,9 +192,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -547,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
@@ -557,28 +554,28 @@
     <col min="5" max="5" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="39" customHeight="1">
+    <row r="1" spans="1:14" ht="39" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:15" ht="26.1" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:14" ht="26.1" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="29.4" customHeight="1">
+    <row r="4" spans="1:14" ht="29.4" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -594,35 +591,32 @@
       <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -637,23 +631,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="2a5c8a5b-eb47-46c4-89f6-a51ecc7fee24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006DBCC5F39D77D847BF875372F5546BD4" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6faa48a039c133dd080055524442ed20">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2a5c8a5b-eb47-46c4-89f6-a51ecc7fee24" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="64ba79c50f0c7943b1ccaf39c724ddfd" ns3:_="">
     <xsd:import namespace="2a5c8a5b-eb47-46c4-89f6-a51ecc7fee24"/>
@@ -835,8 +812,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="2a5c8a5b-eb47-46c4-89f6-a51ecc7fee24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41F30B8E-5A2B-4D30-91F1-D147D5F191F5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{077B6336-A5F9-43E7-9D7E-2D7447105FB4}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
@@ -848,7 +842,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{077B6336-A5F9-43E7-9D7E-2D7447105FB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41F30B8E-5A2B-4D30-91F1-D147D5F191F5}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>